--- a/senior_design_project_groups.xlsx
+++ b/senior_design_project_groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyson/senior design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-work-folder\Senior-Design-Proposals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0034E7FE-4D1F-A94F-AC19-9CB5102C3864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB5EE91-59AF-4531-9500-5FD450FBFE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{6EE475FF-414F-624A-B057-611460D3211B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6EE475FF-414F-624A-B057-611460D3211B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,17 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>Project / members</t>
+  </si>
+  <si>
+    <t>1 (Group Lead)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,9 +436,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D39EEB-7A3F-284C-AFEC-EF39F64342B5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="8" width="22.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/senior_design_project_groups.xlsx
+++ b/senior_design_project_groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-work-folder\Senior-Design-Proposals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyson/senior design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB5EE91-59AF-4531-9500-5FD450FBFE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80CABF8-BC99-3C4F-9DB8-D43F475E8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6EE475FF-414F-624A-B057-611460D3211B}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17360" xr2:uid="{6EE475FF-414F-624A-B057-611460D3211B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -436,18 +436,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D39EEB-7A3F-284C-AFEC-EF39F64342B5}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
-    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="8" width="22.125" customWidth="1"/>
+    <col min="6" max="8" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,154 +470,184 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/senior_design_project_groups.xlsx
+++ b/senior_design_project_groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tyson/senior design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80CABF8-BC99-3C4F-9DB8-D43F475E8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871D5345-ED3F-0448-9D48-4E9217D2DA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17360" xr2:uid="{6EE475FF-414F-624A-B057-611460D3211B}"/>
   </bookViews>
@@ -39,12 +39,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Project / members</t>
   </si>
   <si>
     <t>1 (Group Lead)</t>
+  </si>
+  <si>
+    <t>Jai Metha</t>
+  </si>
+  <si>
+    <t>Phillip Black</t>
+  </si>
+  <si>
+    <t>Lucas Santucci</t>
+  </si>
+  <si>
+    <t>Mallory Bianchi</t>
+  </si>
+  <si>
+    <t>Jacob McClaugherty</t>
+  </si>
+  <si>
+    <t>Ruhi Kabarwahl</t>
+  </si>
+  <si>
+    <t>Daniel Tompkins</t>
+  </si>
+  <si>
+    <t>Samuel Pagoria</t>
+  </si>
+  <si>
+    <t>dupe-27</t>
+  </si>
+  <si>
+    <t>Julien Devol</t>
+  </si>
+  <si>
+    <t>Ellias Tessema</t>
+  </si>
+  <si>
+    <t>Chapin Mohney</t>
+  </si>
+  <si>
+    <t>Silvia Shenouda</t>
+  </si>
+  <si>
+    <t>Jacob Wolpert</t>
+  </si>
+  <si>
+    <t>Ella Mather</t>
+  </si>
+  <si>
+    <t>TJ Caldwell</t>
+  </si>
+  <si>
+    <t>Paul Blair</t>
+  </si>
+  <si>
+    <t>Dane Czajkowski</t>
+  </si>
+  <si>
+    <t>Hamza Awad</t>
+  </si>
+  <si>
+    <t>Carlos Gomez Zevallos</t>
+  </si>
+  <si>
+    <t>Robert Lawrence</t>
+  </si>
+  <si>
+    <t>Trilok Thadani</t>
+  </si>
+  <si>
+    <t>Siddh Patel</t>
+  </si>
+  <si>
+    <t>Sameeha Huq</t>
+  </si>
+  <si>
+    <t>Omar Rawashdeh</t>
+  </si>
+  <si>
+    <t>Trevor Henegar</t>
+  </si>
+  <si>
+    <t>Ryder Finley</t>
+  </si>
+  <si>
+    <t>Thomas Byrd</t>
+  </si>
+  <si>
+    <t>Aadya Sharma</t>
+  </si>
+  <si>
+    <t>Kylie Norosky</t>
+  </si>
+  <si>
+    <t>Caleb Murray</t>
+  </si>
+  <si>
+    <t>Grant Jennings</t>
+  </si>
+  <si>
+    <t>Noah Barnhart</t>
+  </si>
+  <si>
+    <t>Henry Hill</t>
+  </si>
+  <si>
+    <t>Rushi Patel</t>
+  </si>
+  <si>
+    <t>Harrison Clark</t>
+  </si>
+  <si>
+    <t>Shivam Patel</t>
+  </si>
+  <si>
+    <t>Matthew Ferrari</t>
+  </si>
+  <si>
+    <t>Paul Davis</t>
+  </si>
+  <si>
+    <t>Stefan Smith</t>
+  </si>
+  <si>
+    <t>Peter Hansen</t>
+  </si>
+  <si>
+    <t>Eli Fisk</t>
+  </si>
+  <si>
+    <t>Anthony Monteagudo</t>
+  </si>
+  <si>
+    <t>Andrew Benson</t>
+  </si>
+  <si>
+    <t>Sarah Ahmed</t>
+  </si>
+  <si>
+    <t>Micah Reasonover</t>
+  </si>
+  <si>
+    <t>Erik Bright</t>
+  </si>
+  <si>
+    <t>Briana Leverance</t>
+  </si>
+  <si>
+    <t>Ella Bevins</t>
+  </si>
+  <si>
+    <t>Ian Innes</t>
+  </si>
+  <si>
+    <t>William Gillice</t>
+  </si>
+  <si>
+    <t>Robert Lakatosh</t>
+  </si>
+  <si>
+    <t>Ian Smith</t>
+  </si>
+  <si>
+    <t>Cristian Frutos-Gonzalez</t>
+  </si>
+  <si>
+    <t>Erik Hinson</t>
+  </si>
+  <si>
+    <t>Stokes Durden</t>
+  </si>
+  <si>
+    <t>Dominic Peirano</t>
+  </si>
+  <si>
+    <t>Cheyenne Rice</t>
+  </si>
+  <si>
+    <t>Ethan Clissold</t>
+  </si>
+  <si>
+    <t>Brandon Aldridge</t>
   </si>
 </sst>
 </file>
@@ -436,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0D39EEB-7A3F-284C-AFEC-EF39F64342B5}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -524,11 +704,26 @@
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -545,109 +740,294 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
